--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199989</v>
       </c>
       <c r="B2" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199989</v>
       </c>
       <c r="B2" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -714,16 +714,8 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199989</v>
       </c>
       <c r="B2" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199989</v>
       </c>
       <c r="B2" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6985-2025 artfynd.xlsx
+++ b/artfynd/A 6985-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199989</v>
       </c>
       <c r="B2" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
